--- a/results/result_evaluation_logs/Z_synthIE_base_fe.xlsx
+++ b/results/result_evaluation_logs/Z_synthIE_base_fe.xlsx
@@ -1206,10 +1206,10 @@
         <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -2837,10 +2837,10 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>3</v>
@@ -2908,16 +2908,16 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -2984,16 +2984,16 @@
         <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q33" t="n">
         <v>6</v>
@@ -3677,16 +3677,16 @@
         <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
         <v>5</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -4228,10 +4228,10 @@
         <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
         <v>5</v>
